--- a/chapter-4/outputs/stm/v2/STM-2026-03-21-patient-360.xlsx
+++ b/chapter-4/outputs/stm/v2/STM-2026-03-21-patient-360.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Updated - DMS v1.1 alignment</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
